--- a/downloads/base_completa.xlsx
+++ b/downloads/base_completa.xlsx
@@ -3570,12 +3570,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Ampliación Mega</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ampliación de la capacidad de procesamiento, fraccionamiento y transporte de líquidos del gas natural provenientes de la Cuenca Neuquina. Las obras abarcan instalaciones en Neuquén y el corredor de transporte hasta el complejo de fraccionamiento y exportación de Bahía Blanca, con un aumento proyectado de 1.500 toneladas diarias.</t>
+          <t>Ampliación de un complejo industrial para incrementar la capacidad de producción de Líquidos del Gas Natural (LGN) en 1500 toneladas diarias.  El proyecto contempla nuevas instalaciones en la Planta de Separación de Loma La Lata, la ampliación de la capacidad de transporte del poliducto que atraviesa Neuquén, Río Negro, La Pampa y Buenos Aires, y la expansión de la Planta de Fraccionamiento ubicada en Bahía Blanca.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="D34">
@@ -3588,7 +3593,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Compañía Mega S.A. – Sucursal Dedicada</t>
+          <t>Compañía Mega SA Sucursal Dedicada</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>30-71932893-4</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3601,9 +3611,14 @@
           <t>Midstream</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Construcción de plantas de tratamiento, plantas de separación de líquidos de gas natural, oleoductos, gasoductos y poliductos e instalaciones de almacenamiento</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Neuquén; Río Negro; La Pampa; Buenos Aires</t>
+          <t>Neuquén; La Pampa; Río Negro; Buenos Aires</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3612,30 +3627,56 @@
         </is>
       </c>
       <c r="M34">
-        <v>360</v>
+        <v>365.398669</v>
       </c>
       <c r="N34">
-        <v>360</v>
+        <v>365.398669</v>
+      </c>
+      <c r="O34">
+        <v>359.164361</v>
+      </c>
+      <c r="P34">
+        <v>121.613889</v>
+      </c>
+      <c r="Q34">
+        <v>152.709106</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>274.322995</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>En evaluación</t>
-        </is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="T34">
+        <v>792</v>
+      </c>
+      <c r="U34" s="2">
+        <v>46661</v>
       </c>
       <c r="V34" s="2">
         <v>46099</v>
       </c>
+      <c r="W34" s="2">
+        <v>46231</v>
+      </c>
+      <c r="X34" s="2">
+        <v>46260</v>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Res. 1381/2026</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346397/20260826</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Globaris; EconoJournal; Compañía MEGA; Luis Caputo; auditoría 2026-08-08</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>https://econojournal.com.ar/oilgas/vaca-muerta-mega-se-presenta-al-rigi-con-una-inversion-de-us360-millones-en-su-planta-de-separacion-de-liquidos-del-gas/; https://www.ingenierowhite.com/2026/07/31/mega-obtuvo-la-aprobacion-de-su-proyecto-de-inversion-bajo-el-rigi/; https://x.com/LuisCaputoAR/status/2083255389399744911</t>
+          <t>Res. 1381/2026; Globaris; MECON</t>
         </is>
       </c>
     </row>

--- a/downloads/base_completa.xlsx
+++ b/downloads/base_completa.xlsx
@@ -3755,12 +3755,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Fértil Pampa</t>
+          <t>Fertilizantes</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Construcción de un complejo industrial de amoníaco y urea granulada en Bahía Blanca, provincia de Buenos Aires, a cargo de Fértil Pampa. La planta tendrá dos trenes de urea, instalaciones auxiliares, almacenamiento y logística portuaria, con capacidad prevista de 2,1 millones de toneladas anuales.</t>
+          <t>Construcción, operación y gerenciamiento de dos (2) plantas de producción de urea, cada una con capacidad de tres mil toneladas (3.000 t) por día, con sus correspondientes unidades de granulación, y una planta de amoníaco con capacidad de tres mil cuatrocientas cincuenta toneladas (3.450 t) por día, utilizando como insumo principal el gas natural de Vaca Muerta, a desarrollarse en el Puerto de Ingeniero White, partido de Bahía Blanca, provincia de Buenos Aires.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D36">
@@ -3776,6 +3781,11 @@
           <t>Fértil Pampa S.A.U.</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>30-71875855-2</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Petróleo y Gas</t>
@@ -3783,7 +3793,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Petroquímica / Fertilizantes</t>
+          <t>Petroquímica y Fertilizantes</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Petroquímica y Fertilizantes</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3793,34 +3808,60 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Puerto de Ingeniero White, Bahía Blanca</t>
         </is>
       </c>
       <c r="M36">
-        <v>2400</v>
+        <v>2693</v>
       </c>
       <c r="N36">
-        <v>2400</v>
+        <v>2693</v>
+      </c>
+      <c r="O36">
+        <v>2693</v>
+      </c>
+      <c r="P36">
+        <v>785</v>
+      </c>
+      <c r="Q36">
+        <v>881</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1666</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>En evaluación</t>
-        </is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="T36">
+        <v>12500</v>
+      </c>
+      <c r="U36" s="2">
+        <v>47453</v>
       </c>
       <c r="V36" s="2">
-        <v>46136</v>
+        <v>46237</v>
+      </c>
+      <c r="W36" s="2">
+        <v>46237</v>
+      </c>
+      <c r="X36" s="2">
+        <v>46272</v>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Res. 1468/2026</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346966/20260907</t>
+        </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Globaris; Pampa Energía; International Finance Corporation; El Cronista; La Nación; Luis Caputo; auditoría 2026-08-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>https://ri.pampa.com/en/press-release/pampa-energia-announces-its-entry-into-the-fertilizer-business-with-the-construction-of-latin-americas-largest-urea-plant/; https://disclosures.ifc.org/project-detail/ED/52106/fer-il-p; https://www.cronista.com/negocios/fertil-pampa-se-presenta-al-rigi-con-una-inversion-de-us-2400-millones-para-producir-fertilizantes/; https://www.lanacion.com.ar/economia/campo/invertiria-us2400-millones-una-empresa-de-marcelo-mindlin-pidio-ingresar-al-rigi-para-producir-nid23042026/</t>
+          <t>Res.1468/2026; MECON</t>
         </is>
       </c>
     </row>

--- a/downloads/base_completa.xlsx
+++ b/downloads/base_completa.xlsx
@@ -3841,7 +3841,7 @@
         <v>47453</v>
       </c>
       <c r="V36" s="2">
-        <v>46237</v>
+        <v>46133</v>
       </c>
       <c r="W36" s="2">
         <v>46237</v>

--- a/downloads/base_completa.xlsx
+++ b/downloads/base_completa.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB42"/>
+  <dimension ref="A1:AB44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE)</t>
+          <t>San Matías Pipeline S.A.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4373,6 +4373,131 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>https://argentina-lng.ypf.com/assets/pdf/ENG-Argentina-LNG-Adhesion-RIGI.pdf; https://www.lanacion.com.ar/economia/un-proyecto-por-us51000-millones-impulsado-por-ypf-solicito-la-adhesion-al-rigi-nid13082026/; https://www.infobae.com/economia/2026/08/13/con-una-inversion-de-usd-50000-millones-ypf-presenta-al-rigi-el-mayor-proyecto-de-su-historia-para-exportar-gas-de-vaca-muerta/; https://dataenergia.ar/gas/argentina-lgn-solicitaron-la-adhesion-formal-al-rigi-para-una-inversion-historica-de-u-s-51-000-millones-202681319370</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nueva planta dentro del complejo industrial de Toyota en Zárate para producir un vehículo electrificado —descripto por el ministro de Economía como 100% electrificado—, con aproximadamente 70% de la producción destinada a exportación.</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>42</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Toyota Argentina S.A. (Argentina)</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Automotriz</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Zárate</t>
+        </is>
+      </c>
+      <c r="M43">
+        <v>1341</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="T43">
+        <v>6200</v>
+      </c>
+      <c r="V43" s="2">
+        <v>46295</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Luis Caputo / Ministerio de Economía (X, 30/09/2026); Reuters (30/09/2026); La Nación / Toyota Argentina (30/09/2026); ARCA / Decreto 105/2026 (19/02/2026)</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>https://x.com/LuisCaputoAR/status/2105382049758523681; https://www.reuters.com/world/asia-pacific/toyota-invest-134-billion-argentina-production-plant-2026-09-30/; https://www.lanacion.com.ar/autos/toyota-invertira-us1341-millones-para-fabricar-un-nuevo-vehiculo-en-la-argentina-nid30092026/; https://biblioteca.afip.gob.ar/dcp/DEC_C_000749_2024_08_22</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PAE Cerro Dragón</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Desarrollo de recuperación terciaria de petróleo convencional en Cerro Dragón: 22 plantas de inyección de polímeros, perforación de 100 pozos productores e inyectores, adecuación de pozos, intervención de otros 600 pozos productores e infraestructura complementaria de superficie. Producción incremental estimada: 46 millones de barriles de petróleo y 30 BCF de gas natural.</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>43</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Pan American Energy (PAE) (Argentina)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Upstream</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Chubut</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Área Cerro Dragón, Cuenca del Golfo San Jorge</t>
+        </is>
+      </c>
+      <c r="M44">
+        <v>1200</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="V44" s="2">
+        <v>46296</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Gobierno del Chubut (01/10/2026); La Nación / PAE (01/10/2026); Reuters / Luis Caputo (01/10/2026)</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>https://noticias.chubut.gob.ar/notas/gobierno/5481/torres-encabezo-en-la-sede-de-la-ocde-el-anuncio-de-una-inversion-de-usd-1200-millones-de-pae-para-cerro-dragon.html; https://www.lanacion.com.ar/economia/pan-american-energy-busca-ingresar-al-rigi-con-una-inversion-de-us1200-millones-para-revitalizar-nid01102026/; https://www.reuters.com/business/energy/pae-invest-12-billion-argentina-oil-field-minister-says-2026-10-01/</t>
         </is>
       </c>
     </row>

--- a/downloads/base_completa.xlsx
+++ b/downloads/base_completa.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB44"/>
+  <dimension ref="A1:AB45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -4498,6 +4498,75 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>https://noticias.chubut.gob.ar/notas/gobierno/5481/torres-encabezo-en-la-sede-de-la-ocde-el-anuncio-de-una-inversion-de-usd-1200-millones-de-pae-para-cerro-dragon.html; https://www.lanacion.com.ar/economia/pan-american-energy-busca-ingresar-al-rigi-con-una-inversion-de-us1200-millones-para-revitalizar-nid01102026/; https://www.reuters.com/business/energy/pae-invest-12-billion-argentina-oil-field-minister-says-2026-10-01/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Pampa Exploración S.A.</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Desarrollo del depósito Lunahuasi de cobre, oro y plata, actualmente en exploración, con perforaciones y una galería de exploración planificada para avanzar hacia su desarrollo minero</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>44</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>NGEx Minerals Ltd. (Canadá)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pampa Exploración S.A.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Minería</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Cobre</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>San Juan</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Departamento Iglesia; Distrito Vicuña</t>
+        </is>
+      </c>
+      <c r="M45">
+        <v>2437</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="V45" s="2">
+        <v>46113</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>NGEx Minerals, 14/05/2026; Panorama Minero, consulta 02/10/2026</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>https://ngexminerals.com/news/ngex-releases-2025-sustainability-summary-122811/; https://www.panorama-minero.com/es/mining-compendium/argentina/project/lunahuasi</t>
         </is>
       </c>
     </row>

--- a/downloads/base_completa.xlsx
+++ b/downloads/base_completa.xlsx
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="M17">
-        <v>12000</v>
+        <v>12400</v>
       </c>
       <c r="N17">
-        <v>12000</v>
+        <v>12400</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -2173,17 +2173,20 @@
           <t>En evaluación</t>
         </is>
       </c>
+      <c r="T17">
+        <v>6990</v>
+      </c>
       <c r="V17" s="2">
         <v>45771</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Globaris; Gobierno de Neuquén; EconoJournal; Luis Caputo; Clarín; auditoría 2026-08-08</t>
+          <t>Globaris; Gobierno de Neuquén; EconoJournal; Luis Caputo; Clarín; La Nación; Bloomberg</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp; https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/; https://x.com/LuisCaputoAR/status/2047621135127269495; https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html</t>
+          <t>https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp; https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/; https://x.com/LuisCaputoAR/status/2047621135127269495; https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html; https://www.lanacion.com.ar/economia/pluspetrol-y-gyp-obtuvieron-el-rigi-para-un-proyecto-de-us12400-millones-en-vaca-muerta-nid02102026/; https://www.bloomberglinea.com/latinoamerica/argentina/pluspetrol-recibe-luz-verde-del-rigi-para-invertir-us12400-millones-en-vaca-muerta/</t>
         </is>
       </c>
     </row>
@@ -4555,9 +4558,6 @@
         <is>
           <t>En evaluación</t>
         </is>
-      </c>
-      <c r="V45" s="2">
-        <v>46113</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>

--- a/downloads/base_completa.xlsx
+++ b/downloads/base_completa.xlsx
@@ -2663,12 +2663,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Planta de Tratamiento Los Toldos</t>
+          <t>UT RIGI LOS TOLDOS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Desarrollo del área no convencional Los Toldos II Este, en Neuquén, con una planta central de procesamiento de crudo, perforación de pozos y sistemas de recolección y evacuación. El proyecto apunta a alcanzar una producción cercana a 70.000 barriles diarios.</t>
+          <t>Desarrollo de hidrocarburos en el área Los Toldos II Este, Vaca Muerta, el cual consiste en la perforación de 380 pozos junto con su infraestructura asociada para el tratamiento de la producción por una capacidad máxima de 70 mil barriles de petróleo diarios. El proyecto prevé un total de 360 millones de barriles de petróleo de exportación durante su operación.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D24">
@@ -2681,7 +2686,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tecpetrol S.A – Gas y Petróleo del Neuquén S.A. (UT)</t>
+          <t>Tecpetrol S.A. Gas y Petróleo del Neuquén S.A. UT RIGI Los Toldos U.T.E.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>33-71889684-9</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2694,6 +2704,11 @@
           <t>Upstream</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Explotación y producción de nuevos desarrollos de hidrocarburos líquidos y gaseosos costa adentro</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Neuquén</t>
@@ -2701,34 +2716,62 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Departamento Pehuenches; área Los Toldos II Este; Engolfamiento/Bajo de Añelo</t>
         </is>
       </c>
       <c r="M24">
-        <v>6391</v>
+        <v>6432</v>
       </c>
       <c r="N24">
-        <v>6391</v>
+        <v>6432</v>
+      </c>
+      <c r="P24">
+        <v>1182.281332</v>
+      </c>
+      <c r="Q24">
+        <v>577.9334679999999</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1760.2148</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>En evaluación</t>
-        </is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="T24">
+        <v>7900</v>
+      </c>
+      <c r="U24" s="2">
+        <v>46630</v>
       </c>
       <c r="V24" s="2">
-        <v>46118</v>
+        <v>46101</v>
+      </c>
+      <c r="W24" s="2">
+        <v>46274</v>
+      </c>
+      <c r="X24" s="2">
+        <v>46304</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Res. 1771/2026</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/348768/20261009</t>
+        </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Globaris; Techint Ingeniería y Construcción; Vaca Muerta News; Infobae; auditoría 2026-08-08</t>
+          <t>Res. 1771/2026; Tecpetrol</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>https://www.techint.com/es/nuestros-proyectos/los-toldos-ii-este; https://vacamuertanews.com/amp/a-30-km-de-rincon-de-los-sauces-tecpetrol-y-gyp-lanzan-un-megaproyecto-de-shale-oil-con-380-pozos.htm; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.argentina.gob.ar/normativa/nacional/norma-431089 ; https://www.tecpetrol.com/es/noticias/2026/rigi-los-toldos-ii-este</t>
         </is>
       </c>
     </row>

--- a/downloads/base_completa.xlsx
+++ b/downloads/base_completa.xlsx
@@ -3049,7 +3049,7 @@
         <v>47330</v>
       </c>
       <c r="V27" s="2">
-        <v>45595</v>
+        <v>45978</v>
       </c>
       <c r="W27" s="2">
         <v>46185</v>

--- a/downloads/base_completa.xlsx
+++ b/downloads/base_completa.xlsx
@@ -2123,7 +2123,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Desarrollo no convencional de petróleo y gas en los bloques Bajo del Choique–La Invernada, en Vaca Muerta. Contempla la perforación de más de 600 pozos, plantas de procesamiento, ductos e infraestructura asociada, con objetivos de hasta 100.000 barriles diarios de petróleo y 12 millones de m³ diarios de gas.</t>
+          <t>Exploración, producción, tratamiento y transporte de hidrocarburos en un área aproximada de 400 km² del centro-norte de Neuquén. El alcance comprende 620 pozos horizontales, cuatro plantas de tratamiento temprano (EPF), un oleoducto de 45 km y un gasoducto de 20 km, con capacidad total de 100.000 barriles diarios de petróleo y 12 millones de Sm³ diarios de gas. La primera etapa prevé 206 pozos y las EPF 1 y 2; la segunda, 414 pozos y las EPF 3 y 4.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D17">
@@ -2136,7 +2141,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pluspetrol Cuenca Neuquina S.R.L.</t>
+          <t>Gas y Petróleo del Neuquén S.A. - Pluspetrol Cuenca Neuquina S.R.L. – Unión Transitoria Exploración y Producción Bajo del Choique – La Invernada</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>30-71920381-3</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2149,6 +2159,11 @@
           <t>Upstream</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Explotación y producción de nuevos desarrollos de hidrocarburos líquidos y gaseosos costa adentro, con instalaciones complementarias de tratamiento y transporte</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Neuquén</t>
@@ -2156,37 +2171,62 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Centro-norte de Neuquén, aproximadamente 40 km al sur de Rincón de los Sauces; Hub Norte de la Cuenca Neuquina</t>
         </is>
       </c>
       <c r="M17">
-        <v>12400</v>
+        <v>12240</v>
       </c>
       <c r="N17">
-        <v>12400</v>
+        <v>12240</v>
+      </c>
+      <c r="P17">
+        <v>635</v>
+      </c>
+      <c r="Q17">
+        <v>892</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1527</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Aprobado</t>
         </is>
       </c>
       <c r="T17">
-        <v>6990</v>
+        <v>2301</v>
+      </c>
+      <c r="U17" s="2">
+        <v>47238</v>
       </c>
       <c r="V17" s="2">
-        <v>45771</v>
+        <v>46135</v>
+      </c>
+      <c r="W17" s="2">
+        <v>46275</v>
+      </c>
+      <c r="X17" s="2">
+        <v>46314</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Res. 1808/2026</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349233/20261019</t>
+        </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Globaris; Gobierno de Neuquén; EconoJournal; Luis Caputo; Clarín; La Nación; Bloomberg</t>
+          <t>Res. 1808/2026; Gobierno de la Provincia del Neuquén; Casa Rosada</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp; https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/; https://x.com/LuisCaputoAR/status/2047621135127269495; https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html; https://www.lanacion.com.ar/economia/pluspetrol-y-gyp-obtuvieron-el-rigi-para-un-proyecto-de-us12400-millones-en-vaca-muerta-nid02102026/; https://www.bloomberglinea.com/latinoamerica/argentina/pluspetrol-recibe-luz-verde-del-rigi-para-invertir-us12400-millones-en-vaca-muerta/</t>
+          <t>https://www.argentina.gob.ar/normativa/nacional/norma-431356; https://www.neuqueninforma.gob.ar/noticias/2026/10/19/265814-vaca-muerta-acelera-su-expansion-aprobaron-el-ingreso-al-rigi-de-un-proyecto-de-12-mil-millones-de-dolares; https://www.casarosada.gob.ar/informacion/conferencias/51404-conferencia-de-prensa-del-vocero-presidencial-adrian-ravier-desde-casa-rosada-19-10-2026</t>
         </is>
       </c>
     </row>

--- a/downloads/base_completa.xlsx
+++ b/downloads/base_completa.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB45"/>
+  <dimension ref="A1:AB47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Consiste en la construcción y desarrollo de un oleoducto, Iincrementar la capacidad de transporte y almacenamiento de petróleo crudo viabilizando la exportación de hidrocarburos provenientes de la formación “Vaca Muerta”</t>
+          <t>Consiste en la construcción y desarrollo de un oleoducto, incrementar la capacidad de transporte y almacenamiento de petróleo crudo viabilizando la exportación de hidrocarburos provenientes de la formación “Vaca Muerta”</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2018,9 +2018,6 @@
       <c r="M15">
         <v>726</v>
       </c>
-      <c r="N15">
-        <v>726</v>
-      </c>
       <c r="R15">
         <v>0</v>
       </c>
@@ -2090,9 +2087,6 @@
       <c r="M16">
         <v>232</v>
       </c>
-      <c r="N16">
-        <v>232</v>
-      </c>
       <c r="R16">
         <v>0</v>
       </c>
@@ -2390,9 +2384,6 @@
       <c r="M19">
         <v>380</v>
       </c>
-      <c r="N19">
-        <v>380</v>
-      </c>
       <c r="R19">
         <v>0</v>
       </c>
@@ -2462,9 +2453,6 @@
       <c r="M20">
         <v>9500</v>
       </c>
-      <c r="N20">
-        <v>9500</v>
-      </c>
       <c r="R20">
         <v>0</v>
       </c>
@@ -2534,9 +2522,6 @@
       <c r="M21">
         <v>13800</v>
       </c>
-      <c r="N21">
-        <v>13800</v>
-      </c>
       <c r="R21">
         <v>0</v>
       </c>
@@ -2606,9 +2591,6 @@
       <c r="M22">
         <v>200</v>
       </c>
-      <c r="N22">
-        <v>200</v>
-      </c>
       <c r="R22">
         <v>0</v>
       </c>
@@ -2675,9 +2657,6 @@
       <c r="M23">
         <v>206</v>
       </c>
-      <c r="N23">
-        <v>206</v>
-      </c>
       <c r="R23">
         <v>0</v>
       </c>
@@ -2862,9 +2841,6 @@
       <c r="M25">
         <v>4245</v>
       </c>
-      <c r="N25">
-        <v>4245</v>
-      </c>
       <c r="R25">
         <v>0</v>
       </c>
@@ -3160,9 +3136,6 @@
       <c r="M28">
         <v>818</v>
       </c>
-      <c r="N28">
-        <v>818</v>
-      </c>
       <c r="R28">
         <v>0</v>
       </c>
@@ -3453,9 +3426,6 @@
       <c r="M31">
         <v>1000</v>
       </c>
-      <c r="N31">
-        <v>1000</v>
-      </c>
       <c r="R31">
         <v>0</v>
       </c>
@@ -3633,9 +3603,6 @@
       <c r="M33">
         <v>273</v>
       </c>
-      <c r="N33">
-        <v>273</v>
-      </c>
       <c r="R33">
         <v>0</v>
       </c>
@@ -3813,9 +3780,6 @@
       <c r="M35">
         <v>4000</v>
       </c>
-      <c r="N35">
-        <v>4000</v>
-      </c>
       <c r="R35">
         <v>0</v>
       </c>
@@ -4224,9 +4188,6 @@
       <c r="M39">
         <v>1151</v>
       </c>
-      <c r="N39">
-        <v>1151</v>
-      </c>
       <c r="R39">
         <v>0</v>
       </c>
@@ -4296,9 +4257,6 @@
       <c r="M40">
         <v>25000</v>
       </c>
-      <c r="N40">
-        <v>25000</v>
-      </c>
       <c r="R40">
         <v>0</v>
       </c>
@@ -4368,9 +4326,6 @@
       <c r="M41">
         <v>5800</v>
       </c>
-      <c r="N41">
-        <v>5800</v>
-      </c>
       <c r="R41">
         <v>0</v>
       </c>
@@ -4470,7 +4425,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nueva planta dentro del complejo industrial de Toyota en Zárate para producir un vehículo electrificado —descripto por el ministro de Economía como 100% electrificado—, con aproximadamente 70% de la producción destinada a exportación.</t>
+          <t>Ampliación de la planta industrial de Toyota en Zárate mediante la construcción, instalación, puesta en funcionamiento y operación de una tercera planta para fabricar un vehículo híbrido eléctrico no enchufable (full HEV), inicialmente tipo pick-up y con posibilidad de versión SUV.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="D43">
@@ -4481,6 +4441,16 @@
           <t>Toyota Argentina S.A. (Argentina)</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Toyota Argentina S.A. Sucursal Dedicada</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>30-71944240-0</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Tecnología</t>
@@ -4489,6 +4459,11 @@
       <c r="I43" t="inlineStr">
         <is>
           <t>Automotriz</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Fabricación, ensamblado y montaje de vehículos de nueva tecnología de motorización</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4504,25 +4479,59 @@
       <c r="M43">
         <v>1341</v>
       </c>
+      <c r="N43">
+        <v>1252.926108</v>
+      </c>
+      <c r="O43">
+        <v>1252.926108</v>
+      </c>
+      <c r="P43">
+        <v>19.5</v>
+      </c>
+      <c r="Q43">
+        <v>147.753031</v>
+      </c>
+      <c r="R43">
+        <v>167.253031</v>
+      </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Aprobado</t>
         </is>
       </c>
       <c r="T43">
-        <v>6200</v>
+        <v>6225</v>
+      </c>
+      <c r="U43" s="2">
+        <v>47026</v>
       </c>
       <c r="V43" s="2">
-        <v>46295</v>
+        <v>46181</v>
+      </c>
+      <c r="W43" s="2">
+        <v>46294</v>
+      </c>
+      <c r="X43" s="2">
+        <v>46317</v>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Res. 1848/2026</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349428/20261022</t>
+        </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Luis Caputo / Ministerio de Economía (X, 30/09/2026); Reuters (30/09/2026); La Nación / Toyota Argentina (30/09/2026); ARCA / Decreto 105/2026 (19/02/2026)</t>
+          <t>Res. 1848/2026 (B.O. 22/10/2026); Luis Caputo / Ministerio de Economía (X, 30/09/2026); Reuters (30/09/2026); La Nación / Toyota Argentina (30/09/2026)</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>https://x.com/LuisCaputoAR/status/2105382049758523681; https://www.reuters.com/world/asia-pacific/toyota-invest-134-billion-argentina-production-plant-2026-09-30/; https://www.lanacion.com.ar/autos/toyota-invertira-us1341-millones-para-fabricar-un-nuevo-vehiculo-en-la-argentina-nid30092026/; https://biblioteca.afip.gob.ar/dcp/DEC_C_000749_2024_08_22</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349428/20261022; https://x.com/LuisCaputoAR/status/2105382049758523681; https://www.reuters.com/world/asia-pacific/toyota-invest-134-billion-argentina-production-plant-2026-09-30/; https://www.lanacion.com.ar/autos/toyota-invertira-us1341-millones-para-fabricar-un-nuevo-vehiculo-en-la-argentina-nid30092026/</t>
         </is>
       </c>
     </row>
@@ -4650,6 +4659,132 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>https://ngexminerals.com/news/ngex-releases-2025-sustainability-summary-122811/; https://www.panorama-minero.com/es/mining-compendium/argentina/project/lunahuasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Procesamiento de NGLs en Tratayén</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Construcción de un gasoducto de segregación de corrientes de aproximadamente 100 km y nuevas instalaciones de procesamiento en Tratayén, con capacidad para 43 millones de m³ diarios, para separar líquidos del gas natural. Integra un paquete de dos proyectos de TGS con inversión conjunta superior a USD 3.200 millones; el monto actualizado por VPU no fue publicado.</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>45</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Transportadora de Gas del Sur S.A. (TGS) (Argentina)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Procesadora de Gas del Sur S.A. (PGS)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Midstream</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Neuquén</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Tratayén, Neuquén</t>
+        </is>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Luis Caputo / Ministerio de Economía (X, 19/10/2026); Shale24 (19/10/2026); TGS, estados financieros 2T 2026 (04/08/2026)</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>https://x.com/LuisCaputoAR/status/2112170371310858454; https://www.shale24.com/oil-gas/tgs-entra-rigi-us-3200-millones-bahia-blanca-ya-suma-dos-obras-liquidos-vaca-muerta-regimen-n1864; https://api.mziq.com/mzfilemanager/v2/d/78ce1f91-b610-429f-b020-add32c211c1f/dcfe21a3-8a28-44d7-5aeb-2e1a49a861e2?origin=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Poliducto Tratayén–Bahía Blanca y complejo NGL Puerto Galván</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Construcción de un poliducto de 577 km desde Tratayén hasta Bahía Blanca, una planta de fraccionamiento, instalaciones de almacenamiento y obras en la terminal marítima de Puerto Galván para exportar aproximadamente 2,7 millones de toneladas anuales de propano, butano y gasolina natural. Integra un paquete de dos proyectos de TGS con inversión conjunta superior a USD 3.200 millones; el monto actualizado por VPU no fue publicado.</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>46</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Transportadora de Gas del Sur S.A. (TGS) (Argentina)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Midstream de Gas del Sur S.A. (MGS)</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Midstream</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Neuquén; Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Tratayén–Bahía Blanca / Puerto Galván</t>
+        </is>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Luis Caputo / Ministerio de Economía (X, 19/10/2026); Shale24 (19/10/2026); TGS, estados financieros 2T 2026 (04/08/2026)</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>https://x.com/LuisCaputoAR/status/2112170371310858454; https://www.shale24.com/oil-gas/tgs-entra-rigi-us-3200-millones-bahia-blanca-ya-suma-dos-obras-liquidos-vaca-muerta-regimen-n1864; https://api.mziq.com/mzfilemanager/v2/d/78ce1f91-b610-429f-b020-add32c211c1f/dcfe21a3-8a28-44d7-5aeb-2e1a49a861e2?origin=2</t>
         </is>
       </c>
     </row>

--- a/downloads/base_completa.xlsx
+++ b/downloads/base_completa.xlsx
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rincón Mining Pty Ltd.</t>
+          <t>RIGI - RINCON MINING PTY LIMITED</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>30-70708643-9</t>
+          <t>30-71899954-1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2018,9 +2018,6 @@
       <c r="M15">
         <v>726</v>
       </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -2087,9 +2084,6 @@
       <c r="M16">
         <v>232</v>
       </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -2384,9 +2378,6 @@
       <c r="M19">
         <v>380</v>
       </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -2453,9 +2444,6 @@
       <c r="M20">
         <v>9500</v>
       </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -2520,10 +2508,7 @@
         </is>
       </c>
       <c r="M21">
-        <v>13800</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2591,9 +2576,6 @@
       <c r="M22">
         <v>200</v>
       </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -2657,9 +2639,6 @@
       <c r="M23">
         <v>206</v>
       </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -2841,9 +2820,6 @@
       <c r="M25">
         <v>4245</v>
       </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
       <c r="S25" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -3136,9 +3112,6 @@
       <c r="M28">
         <v>818</v>
       </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -3426,9 +3399,6 @@
       <c r="M31">
         <v>1000</v>
       </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
       <c r="S31" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -3603,9 +3573,6 @@
       <c r="M33">
         <v>273</v>
       </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
       <c r="S33" t="inlineStr">
         <is>
           <t>Rechazado</t>
@@ -3736,12 +3703,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Minera Agua Rica (MARA)</t>
+          <t>Minera Agua Rica</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Desarrollo de una mina de cobre, oro, plata y molibdeno en Catamarca, integrando el yacimiento Agua Rica con la infraestructura existente de Alumbrera, ubicada a unos 35 km. El esquema MARA contempla explotación, procesamiento y uso de instalaciones compartidas para producción destinada principalmente a exportación.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="D35">
@@ -3757,6 +3729,11 @@
           <t>Minera Agua Rica LLC Sucursal Argentina</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>30-70769036-0</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Minería</t>
@@ -3767,6 +3744,11 @@
           <t>Cobre</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Minerales de primera y segunda categoría del Código de Minería de la Nación (excluidos potasio y litio)</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Catamarca</t>
@@ -3778,27 +3760,61 @@
         </is>
       </c>
       <c r="M35">
-        <v>4000</v>
+        <v>6394</v>
+      </c>
+      <c r="N35">
+        <v>6393.631995</v>
+      </c>
+      <c r="O35">
+        <v>3310.574165</v>
+      </c>
+      <c r="P35">
+        <v>111.63955213</v>
+      </c>
+      <c r="Q35">
+        <v>659.8944598</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>771.53401193</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>En evaluación</t>
-        </is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="T35">
+        <v>8200</v>
+      </c>
+      <c r="U35" s="2">
+        <v>47118</v>
       </c>
       <c r="V35" s="2">
         <v>45887</v>
       </c>
+      <c r="W35" s="2">
+        <v>46295</v>
+      </c>
+      <c r="X35" s="2">
+        <v>46322</v>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Res. 1854/2026</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349616/20261027</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Globaris; Glencore; Luis Caputo; Reuters; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; Glencore; Luis Caputo; Reuters; Res. 1854/2026; Boletín Oficial; TN</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.boletinoficial.gob.ar/detalleAviso/primera/349616/20261027; https://www.cda.org.ar/detalle_normativa.php?id=9497; https://tn.com.ar/economia/2026/10/27/el-gobierno-aprobo-el-ingreso-al-rigi-de-un-proyecto-minero-de-us6393-millones-en-catamarca/?outputType=amp</t>
         </is>
       </c>
     </row>
@@ -4188,9 +4204,6 @@
       <c r="M39">
         <v>1151</v>
       </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
       <c r="S39" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -4257,9 +4270,6 @@
       <c r="M40">
         <v>25000</v>
       </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -4326,9 +4336,6 @@
       <c r="M41">
         <v>5800</v>
       </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
       <c r="S41" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -4395,9 +4402,6 @@
       <c r="M42">
         <v>51000</v>
       </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -4643,9 +4647,6 @@
       <c r="M45">
         <v>2437</v>
       </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
       <c r="S45" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -4706,9 +4707,6 @@
           <t>Tratayén, Neuquén</t>
         </is>
       </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -4768,9 +4766,6 @@
         <is>
           <t>Tratayén–Bahía Blanca / Puerto Galván</t>
         </is>
-      </c>
-      <c r="R47">
-        <v>0</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
